--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4dd6</t>
+          <t>69e82c69836d7d05c9a0555e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4dd6</t>
+          <t>69efef06ad4799caa7f5e211</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0555e</t>
+          <t>6a04cb3b618f76c4f7b1940f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b1940f</t>
+          <t>6a04cc5b1ef26d534baf3f56</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3f56</t>
+          <t>6a0614def8d6a2fc74348da0</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/837/chiro.xlsx
+++ b/converted_files/837/chiro.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348da0</t>
+          <t>6a32cb6497613a0e49909470</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2085,9 +2085,21 @@
       </c>
       <c r="BR2"/>
       <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
+      <c r="BT2" s="3" t="inlineStr">
+        <is>
+          <t>BALTIMORE</t>
+        </is>
+      </c>
+      <c r="BU2" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="BV2" s="3" t="inlineStr">
+        <is>
+          <t>21236</t>
+        </is>
+      </c>
       <c r="BW2"/>
       <c r="BX2"/>
       <c r="BY2"/>
